--- a/Documentation/Best For Weighting Tables/Best Pets for Tech Savvy Seniors.xlsx
+++ b/Documentation/Best For Weighting Tables/Best Pets for Tech Savvy Seniors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA9751C-CED8-4B35-BB99-F0F57908BD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CD9854-EE10-4464-9BB6-CEB3F75CB1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
+    <workbookView xWindow="6570" yWindow="1680" windowWidth="21600" windowHeight="11295" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Best for Tech-Savvy Seniors" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Feature</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Customization options</t>
   </si>
   <si>
-    <t>Movement Level</t>
-  </si>
-  <si>
     <t>Privacy risk</t>
   </si>
   <si>
@@ -72,13 +69,19 @@
   </si>
   <si>
     <t>Voice Response</t>
+  </si>
+  <si>
+    <t>Fall-risk profile</t>
+  </si>
+  <si>
+    <t>Emotional comfort potential</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,13 +97,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -115,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -127,6 +141,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9351C0-795B-49B9-9D50-FC13AC6BC6DA}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.85546875" style="3" bestFit="1" customWidth="1"/>
@@ -492,7 +509,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -532,7 +549,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="4">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -540,15 +557,29 @@
         <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="4">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <f>SUM(B2:B12)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
